--- a/plantilla_ingresantes.xlsx
+++ b/plantilla_ingresantes.xlsx
@@ -325,90 +325,153 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sedes nuevas y maduración</t>
+          <t xml:space="preserve">El archivo declara sólo ingresantes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
+          <t xml:space="preserve">Los continuadores no se declaran: los genera el modelo. En los resultados aparecen</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
+          <t xml:space="preserve">desglosados en tres grupos según cómo llegan al semestre, y ese desglose sale de la propia</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
+          <t xml:space="preserve">recursión, no de ningún dato de entrada:</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
+          <t xml:space="preserve">  Regulares     se matricularon también el semestre inmediato anterior.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
+          <t xml:space="preserve">  Reiniciados   interrumpieron un semestre y volvieron.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">semestre en que aparezca en esta hoja.</t>
+          <t xml:space="preserve">  Recuperados   interrumpieron dos o más semestres y volvieron.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conviene mirarlos por separado al planificar: un reiniciado repite ciclo el doble que un</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nomenclatura de semestres</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Último semestre observado en la base</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-II</t>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regular y tiene mucha menos probabilidad de seguir el semestre siguiente.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Primer semestre proyectable</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-I</t>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sedes nuevas y maduración</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semestre en que aparezca en esta hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nomenclatura de semestres</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Último semestre observado en la base</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-II</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primer semestre proyectable</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-I</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Formato</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t xml:space="preserve">AAAA-I (primer semestre) · AAAA-II (segundo semestre)</t>
         </is>

--- a/plantilla_ingresantes.xlsx
+++ b/plantilla_ingresantes.xlsx
@@ -353,125 +353,146 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Regulares     se matricularon también el semestre inmediato anterior.</t>
+          <t xml:space="preserve">  Regulares     se matricularon también el semestre anterior y cambiaron de ciclo.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Reiniciados   interrumpieron un semestre y volvieron.</t>
+          <t xml:space="preserve">  Recuperados   se matricularon también el semestre anterior, pero vuelven al MISMO ciclo:</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Recuperados   interrumpieron dos o más semestres y volvieron.</t>
+          <t xml:space="preserve">                perdieron el que cursaban y lo retoman.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conviene mirarlos por separado al planificar: un reiniciado repite ciclo el doble que un</t>
+          <t xml:space="preserve">  Reiniciados   interrumpieron uno o más semestres y volvieron a matricularse.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">regular y tiene mucha menos probabilidad de seguir el semestre siguiente.</t>
+          <t xml:space="preserve">Conviene mirarlos por separado al planificar, porque el riesgo no es el mismo: el</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reiniciado se cae de la matrícula (continúa el 58 % frente al 86 % de un regular) y el</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sedes nuevas y maduración</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recuperado se queda, pero no avanza (sólo el 57 % cambia de ciclo, y uno de cada cinco</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
+          <t xml:space="preserve">repite otra vez), de modo que se acumula en los ciclos bajos.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sedes nuevas y maduración</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
+          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
+          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">semestre en que aparezca en esta hoja.</t>
+          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nomenclatura de semestres</t>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t xml:space="preserve">semestre en que aparezca en esta hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nomenclatura de semestres</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Último semestre observado en la base</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-II</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t xml:space="preserve">Primer semestre proyectable</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-I</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-I</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t xml:space="preserve">Formato</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t xml:space="preserve">AAAA-I (primer semestre) · AAAA-II (segundo semestre)</t>
         </is>

--- a/plantilla_ingresantes.xlsx
+++ b/plantilla_ingresantes.xlsx
@@ -388,7 +388,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">reiniciado se cae de la matrícula (continúa el 58 % frente al 86 % de un regular) y el</t>
+          <t xml:space="preserve">reiniciado se cae de la matrícula (continúa el 59 % frente al 86 % de un regular) y el</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="F141">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="142">
@@ -4496,7 +4496,7 @@
         <v>1</v>
       </c>
       <c r="F142">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="143">
@@ -4524,7 +4524,7 @@
         <v>1</v>
       </c>
       <c r="F143">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="144">
@@ -4552,7 +4552,7 @@
         <v>1</v>
       </c>
       <c r="F144">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="145">
@@ -4580,7 +4580,7 @@
         <v>1</v>
       </c>
       <c r="F145">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="146">
@@ -4608,7 +4608,7 @@
         <v>1</v>
       </c>
       <c r="F146">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="147">
@@ -4636,7 +4636,7 @@
         <v>1</v>
       </c>
       <c r="F147">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="148">
@@ -4664,7 +4664,7 @@
         <v>1</v>
       </c>
       <c r="F148">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="149">
@@ -4748,7 +4748,7 @@
         <v>1</v>
       </c>
       <c r="F151">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="152">
@@ -4776,7 +4776,7 @@
         <v>1</v>
       </c>
       <c r="F152">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="153">
@@ -4804,7 +4804,7 @@
         <v>1</v>
       </c>
       <c r="F153">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="154">
@@ -4860,7 +4860,7 @@
         <v>1</v>
       </c>
       <c r="F155">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="156">
@@ -4876,19 +4876,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBSTETRICIA</t>
+          <t xml:space="preserve">DERECHO</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presencial</t>
+          <t xml:space="preserve">Semi Presencial</t>
         </is>
       </c>
       <c r="E156">
         <v>1</v>
       </c>
       <c r="F156">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="157">
@@ -4904,19 +4904,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+          <t xml:space="preserve">OBSTETRICIA</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">A distancia</t>
+          <t xml:space="preserve">Presencial</t>
         </is>
       </c>
       <c r="E157">
         <v>1</v>
       </c>
       <c r="F157">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="158">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presencial</t>
+          <t xml:space="preserve">A distancia</t>
         </is>
       </c>
       <c r="E158">
         <v>1</v>
       </c>
       <c r="F158">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="159">
@@ -4960,19 +4960,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semi Presencial</t>
+          <t xml:space="preserve">Presencial</t>
         </is>
       </c>
       <c r="E159">
         <v>1</v>
       </c>
       <c r="F159">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="160">
@@ -4988,19 +4988,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semi Presencial</t>
+          <t xml:space="preserve">A distancia</t>
         </is>
       </c>
       <c r="E160">
         <v>1</v>
       </c>
       <c r="F160">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="161">
@@ -5016,19 +5016,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presencial</t>
+          <t xml:space="preserve">Semi Presencial</t>
         </is>
       </c>
       <c r="E161">
         <v>1</v>
       </c>
       <c r="F161">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="162">
@@ -5039,24 +5039,24 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+          <t xml:space="preserve">DERECHO</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">A distancia</t>
+          <t xml:space="preserve">Semi Presencial</t>
         </is>
       </c>
       <c r="E162">
         <v>1</v>
       </c>
       <c r="F162">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="163">
@@ -5072,19 +5072,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
+          <t xml:space="preserve">DERECHO</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">A distancia</t>
+          <t xml:space="preserve">Presencial</t>
         </is>
       </c>
       <c r="E163">
         <v>1</v>
       </c>
       <c r="F163">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="164">
@@ -5100,19 +5100,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+          <t xml:space="preserve">CONTABILIDAD</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semi Presencial</t>
+          <t xml:space="preserve">A distancia</t>
         </is>
       </c>
       <c r="E164">
         <v>1</v>
       </c>
       <c r="F164">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="165">
@@ -5128,19 +5128,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presencial</t>
+          <t xml:space="preserve">Semi Presencial</t>
         </is>
       </c>
       <c r="E165">
         <v>1</v>
       </c>
       <c r="F165">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="166">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5168,7 +5168,7 @@
         <v>1</v>
       </c>
       <c r="F166">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="167">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+          <t xml:space="preserve">PSICOLOGÍA</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5196,7 +5196,7 @@
         <v>1</v>
       </c>
       <c r="F167">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="168">
@@ -5207,24 +5207,24 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSICOLOGÍA</t>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semi Presencial</t>
+          <t xml:space="preserve">Presencial</t>
         </is>
       </c>
       <c r="E168">
         <v>1</v>
       </c>
       <c r="F168">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="169">
@@ -5280,7 +5280,7 @@
         <v>1</v>
       </c>
       <c r="F170">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="171">
@@ -5308,7 +5308,7 @@
         <v>1</v>
       </c>
       <c r="F171">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="172">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5336,7 +5336,7 @@
         <v>1</v>
       </c>
       <c r="F172">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="173">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5364,7 +5364,7 @@
         <v>1</v>
       </c>
       <c r="F173">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="174">
@@ -5392,7 +5392,7 @@
         <v>1</v>
       </c>
       <c r="F174">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="175">
@@ -5420,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="F175">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="176">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">CIENCIAS DE LA COMUNICACIÓN</t>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+          <t xml:space="preserve">CIENCIAS DE LA COMUNICACIÓN</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5644,7 +5644,7 @@
         <v>1</v>
       </c>
       <c r="F183">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="184">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
+          <t xml:space="preserve">ARQUITECTURA</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
+          <t xml:space="preserve">DERECHO</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5784,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="F188">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="189">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARQUITECTURA</t>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5952,7 +5952,7 @@
         <v>1</v>
       </c>
       <c r="F194">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="195">
@@ -5963,24 +5963,24 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+          <t xml:space="preserve">CONTABILIDAD</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presencial</t>
+          <t xml:space="preserve">Semi Presencial</t>
         </is>
       </c>
       <c r="E195">
         <v>1</v>
       </c>
       <c r="F195">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196">
@@ -5996,19 +5996,19 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semi Presencial</t>
+          <t xml:space="preserve">Presencial</t>
         </is>
       </c>
       <c r="E196">
         <v>1</v>
       </c>
       <c r="F196">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="197">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -6036,7 +6036,7 @@
         <v>1</v>
       </c>
       <c r="F197">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -6064,7 +6064,7 @@
         <v>1</v>
       </c>
       <c r="F198">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="199">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
+          <t xml:space="preserve">DERECHO</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="E199">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F199">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="200">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARQUITECTURA</t>
+          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semi Presencial</t>
+          <t xml:space="preserve">A distancia</t>
         </is>
       </c>
       <c r="E200">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
+          <t xml:space="preserve">ARQUITECTURA</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -6164,16 +6164,16 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
+          <t xml:space="preserve">CONTABILIDAD</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">A distancia</t>
+          <t xml:space="preserve">Semi Presencial</t>
         </is>
       </c>
       <c r="E202">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F202">
         <v>17</v>
@@ -6327,17 +6327,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presencial</t>
+          <t xml:space="preserve">Semi Presencial</t>
         </is>
       </c>
       <c r="E208">
@@ -6360,19 +6360,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+          <t xml:space="preserve">CONTABILIDAD</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semi Presencial</t>
+          <t xml:space="preserve">Presencial</t>
         </is>
       </c>
       <c r="E209">
         <v>1</v>
       </c>
       <c r="F209">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="210">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6400,7 +6400,7 @@
         <v>1</v>
       </c>
       <c r="F210">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="211">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="E215">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F215">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="216">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6593,7 +6593,7 @@
         </is>
       </c>
       <c r="E217">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F217">
         <v>5</v>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+          <t xml:space="preserve">DERECHO</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="E218">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F218">
         <v>5</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="E219">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F219">
         <v>4</v>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="E220">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F220">
         <v>4</v>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="E223">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F223">
         <v>3</v>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semi Presencial</t>
+          <t xml:space="preserve">A distancia</t>
         </is>
       </c>
       <c r="E224">
@@ -6808,16 +6808,16 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+          <t xml:space="preserve">CONTABILIDAD</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presencial</t>
+          <t xml:space="preserve">Semi Presencial</t>
         </is>
       </c>
       <c r="E225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F225">
         <v>3</v>
@@ -6836,19 +6836,19 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">A distancia</t>
+          <t xml:space="preserve">Presencial</t>
         </is>
       </c>
       <c r="E226">
         <v>2</v>
       </c>
       <c r="F226">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="E227">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F227">
         <v>2</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="E228">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F228">
         <v>2</v>
@@ -6925,11 +6925,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presencial</t>
+          <t xml:space="preserve">A distancia</t>
         </is>
       </c>
       <c r="E229">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F229">
         <v>2</v>
@@ -6953,11 +6953,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semi Presencial</t>
+          <t xml:space="preserve">Presencial</t>
         </is>
       </c>
       <c r="E230">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F230">
         <v>2</v>
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="E231">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F231">
         <v>2</v>
@@ -7004,16 +7004,16 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">A distancia</t>
+          <t xml:space="preserve">Semi Presencial</t>
         </is>
       </c>
       <c r="E232">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F232">
         <v>2</v>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">

--- a/plantilla_ingresantes.xlsx
+++ b/plantilla_ingresantes.xlsx
@@ -198,7 +198,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoria. Ciclo al que ingresa el estudiante (1 en la admisión ordinaria; &gt;1 en traslados y convalidaciones).</t>
+          <t xml:space="preserve">Recomendada. Ciclo al que ingresa el estudiante: 1 en la admisión ordinaria, mayor que 1 en traslados y convalidaciones. Si se omite la columna o la celda, el modelo reparte esa fila entre los ciclos donde el histórico registra convalidaciones.</t>
         </is>
       </c>
     </row>
@@ -276,223 +276,314 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por qué conviene declarar la modalidad</t>
+          <t xml:space="preserve">Si no sabe en qué ciclo entrarán</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">La modalidad cambia el comportamiento del estudiante de forma muy marcada. En el primer</t>
+          <t xml:space="preserve">Deje la columna «Ciclo» vacía —o quítela— y declare sólo el total por semestre, sede,</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ciclo, la continuación al semestre siguiente va del 42 % en la modalidad a distancia al 71 %</t>
+          <t xml:space="preserve">carrera y modalidad. El modelo lo reparte con las tasas del histórico, que separa en:</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">en la presencial, con la semipresencial en medio (56 %). También determina casi por completo</t>
+          <t xml:space="preserve">  NIVEL   cuántos entran por encima del ciclo 1. Va del 0,2 % de Obstetricia al 19,7 % de</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">el turno: a distancia es noche en un 90 %, mientras que presencial es mañana en un 77 %.</t>
+          <t xml:space="preserve">          Contabilidad, y es más del doble en las modalidades no presenciales. Depende</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Si la columna se deja vacía el modelo estima el reparto, pero la composición está en fuerte</t>
+          <t xml:space="preserve">          además de la paridad del semestre: en los segundos semestres la cuota sube,</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">deriva —a distancia pasó del 4,8 % al 19,6 % de la matrícula— y esa estimación arrastra error.</t>
+          <t xml:space="preserve">          porque lo que baja es la campaña de ciclo 1, no el número de convalidados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FORMA   a qué ciclo llegan. Es casi universal: 57 % al ciclo 2, 21 % al 3, 13 % al 4</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El archivo declara sólo ingresantes</t>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          y 9 % al 5 o más.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los continuadores no se declaran: los genera el modelo. En los resultados aparecen</t>
+          <t xml:space="preserve">El reparto respeta el ciclo terminal del plan y el tope de maduración de una sede nueva,</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">desglosados en tres grupos según cómo llegan al semestre, y ese desglose sale de la propia</t>
+          <t xml:space="preserve">y conserva el total exacto: no se pierde ni se inventa ningún ingresante.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">recursión, no de ningún dato de entrada:</t>
+          <t xml:space="preserve">Conviene declarar el ciclo cuando se conozca: la estimación describe el comportamiento</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Regulares     se matricularon también el semestre anterior y cambiaron de ciclo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Recuperados   se matricularon también el semestre anterior, pero vuelven al MISMO ciclo:</t>
+          <t xml:space="preserve">medio del histórico, no una política de admisión que vaya a cambiar.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                perdieron el que cursaban y lo retoman.</t>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por qué conviene declarar la modalidad</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Reiniciados   interrumpieron uno o más semestres y volvieron a matricularse.</t>
+          <t xml:space="preserve">La modalidad cambia el comportamiento del estudiante de forma muy marcada. En el primer</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conviene mirarlos por separado al planificar, porque el riesgo no es el mismo: el</t>
+          <t xml:space="preserve">ciclo, la continuación al semestre siguiente va del 42 % en la modalidad a distancia al 71 %</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">reiniciado se cae de la matrícula (continúa el 59 % frente al 86 % de un regular) y el</t>
+          <t xml:space="preserve">en la presencial, con la semipresencial en medio (56 %). También determina casi por completo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">recuperado se queda, pero no avanza (sólo el 57 % cambia de ciclo, y uno de cada cinco</t>
+          <t xml:space="preserve">el turno: a distancia es noche en un 90 %, mientras que presencial es mañana en un 77 %.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">repite otra vez), de modo que se acumula en los ciclos bajos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sedes nuevas y maduración</t>
+          <t xml:space="preserve">Si la columna se deja vacía el modelo estima el reparto, pero la composición está en fuerte</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deriva —a distancia pasó del 4,8 % al 19,6 % de la matrícula— y esa estimación arrastra error.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El archivo declara sólo ingresantes</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
+          <t xml:space="preserve">Los continuadores no se declaran: los genera el modelo. En los resultados aparecen</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
+          <t xml:space="preserve">desglosados en tres grupos según cómo llegan al semestre, y ese desglose sale de la propia</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
+          <t xml:space="preserve">recursión, no de ningún dato de entrada:</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
+          <t xml:space="preserve">  Regulares     se matricularon también el semestre anterior y cambiaron de ciclo.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">semestre en que aparezca en esta hoja.</t>
+          <t xml:space="preserve">  Recuperados   se matricularon también el semestre anterior, pero vuelven al MISMO ciclo:</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                perdieron el que cursaban y lo retoman.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nomenclatura de semestres</t>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Reiniciados   interrumpieron uno o más semestres y volvieron a matricularse.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Último semestre observado en la base</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-II</t>
+          <t xml:space="preserve">Conviene mirarlos por separado al planificar, porque el riesgo no es el mismo: el</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primer semestre proyectable</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-I</t>
+          <t xml:space="preserve">reiniciado se cae de la matrícula (continúa el 59 % frente al 86 % de un regular) y el</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t xml:space="preserve">recuperado se queda, pero no avanza (sólo el 57 % cambia de ciclo, y uno de cada cinco</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repite otra vez), de modo que se acumula en los ciclos bajos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sedes nuevas y maduración</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semestre en que aparezca en esta hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nomenclatura de semestres</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Último semestre observado en la base</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-II</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primer semestre proyectable</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-I</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t xml:space="preserve">Formato</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t xml:space="preserve">AAAA-I (primer semestre) · AAAA-II (segundo semestre)</t>
         </is>

--- a/plantilla_ingresantes.xlsx
+++ b/plantilla_ingresantes.xlsx
@@ -269,321 +269,356 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Además despliega su plan ciclo a ciclo desde el semestre en que aparece: en el primero</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sólo imparte el ciclo 1, en el segundo el 1 y el 2, y así sucesivamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Si el plan no dura 10 ciclos, indíquelo en «CiclosPlan».</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Si no sabe en qué ciclo entrarán</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deje la columna «Ciclo» vacía —o quítela— y declare sólo el total por semestre, sede,</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">carrera y modalidad. El modelo lo reparte con las tasas del histórico, que separa en:</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NIVEL   cuántos entran por encima del ciclo 1. Va del 0,2 % de Obstetricia al 19,7 % de</t>
+          <t xml:space="preserve">Deje la columna «Ciclo» vacía —o quítela— y declare sólo el total por semestre, sede,</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Contabilidad, y es más del doble en las modalidades no presenciales. Depende</t>
+          <t xml:space="preserve">carrera y modalidad. El modelo lo reparte con las tasas del histórico, que separa en:</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">          además de la paridad del semestre: en los segundos semestres la cuota sube,</t>
+          <t xml:space="preserve">  NIVEL   cuántos entran por encima del ciclo 1. Va del 0,2 % de Obstetricia al 19,7 % de</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">          porque lo que baja es la campaña de ciclo 1, no el número de convalidados.</t>
+          <t xml:space="preserve">          Contabilidad, y es más del doble en las modalidades no presenciales. Depende</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FORMA   a qué ciclo llegan. Es casi universal: 57 % al ciclo 2, 21 % al 3, 13 % al 4</t>
+          <t xml:space="preserve">          además de la paridad del semestre: en los segundos semestres la cuota sube,</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">          y 9 % al 5 o más.</t>
+          <t xml:space="preserve">          porque lo que baja es la campaña de ciclo 1, no el número de convalidados.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">El reparto respeta el ciclo terminal del plan y el tope de maduración de una sede nueva,</t>
+          <t xml:space="preserve">  FORMA   a qué ciclo llegan. Es casi universal: 57 % al ciclo 2, 21 % al 3, 13 % al 4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">y conserva el total exacto: no se pierde ni se inventa ningún ingresante.</t>
+          <t xml:space="preserve">          y 9 % al 5 o más.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conviene declarar el ciclo cuando se conozca: la estimación describe el comportamiento</t>
+          <t xml:space="preserve">El reparto respeta el ciclo terminal del plan, el tope de maduración de una sede nueva y</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">medio del histórico, no una política de admisión que vaya a cambiar.</t>
+          <t xml:space="preserve">el de un programa nuevo, y conserva el total exacto: no se pierde ni se inventa a nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un programa que no figura en el catálogo empieza a impartirse en el primer semestre en</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por qué conviene declarar la modalidad</t>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">que aparece, de modo que ahí sólo existe el ciclo 1 y todos sus ingresantes van a él;</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">La modalidad cambia el comportamiento del estudiante de forma muy marcada. En el primer</t>
+          <t xml:space="preserve">despliega un ciclo más en cada semestre siguiente, conforme avanza su primera cohorte.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ciclo, la continuación al semestre siguiente va del 42 % en la modalidad a distancia al 71 %</t>
+          <t xml:space="preserve">Conviene declarar el ciclo cuando se conozca: la estimación describe el comportamiento</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">en la presencial, con la semipresencial en medio (56 %). También determina casi por completo</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el turno: a distancia es noche en un 90 %, mientras que presencial es mañana en un 77 %.</t>
+          <t xml:space="preserve">medio del histórico, no una política de admisión que vaya a cambiar.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Si la columna se deja vacía el modelo estima el reparto, pero la composición está en fuerte</t>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por qué conviene declarar la modalidad</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">deriva —a distancia pasó del 4,8 % al 19,6 % de la matrícula— y esa estimación arrastra error.</t>
+          <t xml:space="preserve">La modalidad cambia el comportamiento del estudiante de forma muy marcada. En el primer</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ciclo, la continuación al semestre siguiente va del 42 % en la modalidad a distancia al 71 %</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El archivo declara sólo ingresantes</t>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en la presencial, con la semipresencial en medio (56 %). También determina casi por completo</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los continuadores no se declaran: los genera el modelo. En los resultados aparecen</t>
+          <t xml:space="preserve">el turno: a distancia es noche en un 90 %, mientras que presencial es mañana en un 77 %.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">desglosados en tres grupos según cómo llegan al semestre, y ese desglose sale de la propia</t>
+          <t xml:space="preserve">Si la columna se deja vacía el modelo estima el reparto, pero la composición está en fuerte</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">recursión, no de ningún dato de entrada:</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Regulares     se matricularon también el semestre anterior y cambiaron de ciclo.</t>
+          <t xml:space="preserve">deriva —a distancia pasó del 4,8 % al 19,6 % de la matrícula— y esa estimación arrastra error.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Recuperados   se matricularon también el semestre anterior, pero vuelven al MISMO ciclo:</t>
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El archivo declara sólo ingresantes</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">                perdieron el que cursaban y lo retoman.</t>
+          <t xml:space="preserve">Los continuadores no se declaran: los genera el modelo. En los resultados aparecen</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Reiniciados   interrumpieron uno o más semestres y volvieron a matricularse.</t>
+          <t xml:space="preserve">desglosados en tres grupos según cómo llegan al semestre, y ese desglose sale de la propia</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conviene mirarlos por separado al planificar, porque el riesgo no es el mismo: el</t>
+          <t xml:space="preserve">recursión, no de ningún dato de entrada:</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">reiniciado se cae de la matrícula (continúa el 59 % frente al 86 % de un regular) y el</t>
+          <t xml:space="preserve">  Regulares     se matricularon también el semestre anterior y cambiaron de ciclo.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">recuperado se queda, pero no avanza (sólo el 57 % cambia de ciclo, y uno de cada cinco</t>
+          <t xml:space="preserve">  Recuperados   se matricularon también el semestre anterior, pero vuelven al MISMO ciclo:</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">repite otra vez), de modo que se acumula en los ciclos bajos.</t>
+          <t xml:space="preserve">                perdieron el que cursaban y lo retoman.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Reiniciados   interrumpieron uno o más semestres y volvieron a matricularse.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sedes nuevas y maduración</t>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conviene mirarlos por separado al planificar, porque el riesgo no es el mismo: el</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
+          <t xml:space="preserve">reiniciado se cae de la matrícula (continúa el 59 % frente al 86 % de un regular) y el</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
+          <t xml:space="preserve">recuperado se queda, pero no avanza (sólo el 57 % cambia de ciclo, y uno de cada cinco</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
+          <t xml:space="preserve">repite otra vez), de modo que se acumula en los ciclos bajos.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sedes nuevas y maduración</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">semestre en que aparezca en esta hoja.</t>
+          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nomenclatura de semestres</t>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Último semestre observado en la base</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-II</t>
+          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primer semestre proyectable</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-I</t>
+          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t xml:space="preserve">semestre en que aparezca en esta hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nomenclatura de semestres</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Último semestre observado en la base</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-II</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primer semestre proyectable</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-I</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t xml:space="preserve">Formato</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t xml:space="preserve">AAAA-I (primer semestre) · AAAA-II (segundo semestre)</t>
         </is>

--- a/plantilla_ingresantes.xlsx
+++ b/plantilla_ingresantes.xlsx
@@ -486,7 +486,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Recuperados   se matricularon también el semestre anterior, pero vuelven al MISMO ciclo:</t>
+          <t xml:space="preserve">  Recuperados   se matricularon también el semestre anterior pero NO lo cerraron:</t>
         </is>
       </c>
     </row>
@@ -500,125 +500,139 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Reiniciados   interrumpieron uno o más semestres y volvieron a matricularse.</t>
+          <t xml:space="preserve">                abandono de ciclo, retiro o inhabilitación.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conviene mirarlos por separado al planificar, porque el riesgo no es el mismo: el</t>
+          <t xml:space="preserve">  Reinicio      interrumpieron uno o más semestres y volvieron a matricularse.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">reiniciado se cae de la matrícula (continúa el 59 % frente al 86 % de un regular) y el</t>
+          <t xml:space="preserve">  Ingres. nueva admisión   reingresaron por nueva admisión tras una ausencia larga.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">recuperado se queda, pero no avanza (sólo el 57 % cambia de ciclo, y uno de cada cinco</t>
+          <t xml:space="preserve">Conviene mirarlos por separado al planificar, porque el riesgo no es el mismo: el</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t xml:space="preserve">reinicio se cae de la matrícula (continúa el 61 % frente al 86 % de un regular) y el</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recuperado se queda, pero no avanza (sólo el 49 % cambia de ciclo, y casi dos de cada cinco</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t xml:space="preserve">repite otra vez), de modo que se acumula en los ciclos bajos.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sedes nuevas y maduración</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
+          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
+          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
+          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t xml:space="preserve">semestre en que aparezca en esta hoja.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclatura de semestres</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Último semestre observado en la base</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-II</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Primer semestre proyectable</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Último semestre observado en la base</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-II</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primer semestre proyectable</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-I</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t xml:space="preserve">Formato</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t xml:space="preserve">AAAA-I (primer semestre) · AAAA-II (segundo semestre)</t>
         </is>
